--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-05-2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-tb4000-insulation-board-1200-x-2400mm?variant=55597615874432</t>
+          <t>£14.75</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-tb4025-high-performance-pir-insulation-2400mm-x-1200mm-x-25mm</t>
+          <t>£15.16</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£22.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£60.42</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>£61.67</t>
+          <t>£67.89</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£61.44</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>£62.31</t>
+          <t>Error: ('Connection broken: IncompleteRead(10102 bytes read, 30014 more expected)', IncompleteRead(10102 bytes read, 30014 more expected))</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£62.20</t>
+          <t>Error: ('Connection broken: IncompleteRead(40157 bytes read, 40073 more expected)', IncompleteRead(40157 bytes read, 40073 more expected))</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
